--- a/Result/profitability/9935.xlsx
+++ b/Result/profitability/9935.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.415</v>
+        <v>0.41</v>
       </c>
       <c r="N2" t="n">
-        <v>24.35625</v>
+        <v>24.8925</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.335</v>
+        <v>0.32625</v>
       </c>
       <c r="N3" t="n">
-        <v>22.72125</v>
+        <v>23.1375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0.27125</v>
+        <v>0.28375</v>
       </c>
       <c r="N4" t="n">
-        <v>20.525</v>
+        <v>21.015</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01750000000000002</v>
+        <v>0.12</v>
       </c>
       <c r="N5" t="n">
-        <v>16.7625</v>
+        <v>17.1675</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0675</v>
+        <v>0.05374999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>14.94</v>
+        <v>15.2625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07625</v>
+        <v>-0.07750000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>13.2025</v>
+        <v>13.40125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1625</v>
+        <v>-0.15</v>
       </c>
       <c r="N8" t="n">
-        <v>11.1175</v>
+        <v>11.31625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>-0.2</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.25</v>
+        <v>-0.2500000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>8.55625</v>
@@ -2029,7 +2029,7 @@
         <v>-0.6325000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>9.596250000000001</v>
+        <v>9.59625</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9935</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1351</v>
+      </c>
+      <c r="D75" t="n">
+        <v>960</v>
+      </c>
+      <c r="E75" t="n">
+        <v>390</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="G75" t="n">
+        <v>168</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="J75" t="n">
+        <v>147</v>
+      </c>
+      <c r="K75" t="n">
+        <v>108</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.51125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.3125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.196078431372549</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05826310003664337</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.904761904761905</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.239999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1263650546021839</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
